--- a/artfynd/A 15284-2020 artfynd.xlsx
+++ b/artfynd/A 15284-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15284-2020 artfynd.xlsx
+++ b/artfynd/A 15284-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,142 +1018,6 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI) inför anläggning av nytt reningsverk i Kartåsenområdet, Lidköpings komm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>88957756</v>
-      </c>
-      <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Olofslund-Skogslyckan, N om, Vg</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>392689.4049795267</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6483785.230183859</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Lidköping</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lidköping</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>OV-Lid-0064</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2016-08-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2016-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>vid 1345690 6487319 och 1345692 6487274</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Talldominerad blandskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Oskar Gran, Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
